--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU10/HRM/post DFS_HRM-2031-0220/panel_11/Coupon back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU10_Coupon_Back_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU10/HRM/post DFS_HRM-2031-0220/panel_11/Coupon back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU10_Coupon_Back_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>17.3789</v>
+        <v>17.78538</v>
       </c>
       <c r="D2" t="n">
-        <v>17.24537</v>
+        <v>17.2966</v>
       </c>
       <c r="E2" t="n">
-        <v>17.58091</v>
+        <v>17.36914</v>
       </c>
       <c r="F2" t="n">
-        <v>43.65284</v>
+        <v>45.66222</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05308</v>
+        <v>0.05316</v>
       </c>
       <c r="H2" t="n">
-        <v>1.95453</v>
+        <v>1.93283</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>17.36125</v>
+        <v>18.0782</v>
       </c>
       <c r="D3" t="n">
-        <v>17.18132</v>
+        <v>17.24765</v>
       </c>
       <c r="E3" t="n">
-        <v>17.59858</v>
+        <v>17.59896</v>
       </c>
       <c r="F3" t="n">
-        <v>44.31108</v>
+        <v>43.9937</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0527</v>
+        <v>0.05452</v>
       </c>
       <c r="H3" t="n">
-        <v>1.87776</v>
+        <v>1.85823</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>17.53408</v>
+        <v>17.85587</v>
       </c>
       <c r="D4" t="n">
-        <v>17.32992</v>
+        <v>17.17156</v>
       </c>
       <c r="E4" t="n">
-        <v>17.42073</v>
+        <v>17.33357</v>
       </c>
       <c r="F4" t="n">
-        <v>44.99752</v>
+        <v>44.61298</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05295</v>
+        <v>0.05322</v>
       </c>
       <c r="H4" t="n">
-        <v>1.92635</v>
+        <v>1.88337</v>
       </c>
     </row>
     <row r="5">
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>17.52667</v>
+        <v>18.22369</v>
       </c>
       <c r="D6" t="n">
-        <v>16.89489</v>
+        <v>16.88592</v>
       </c>
       <c r="E6" t="n">
-        <v>17.32181</v>
+        <v>17.54797</v>
       </c>
       <c r="F6" t="n">
-        <v>22.7962</v>
+        <v>23.07152</v>
       </c>
       <c r="G6" t="n">
-        <v>35.72589</v>
+        <v>35.59254</v>
       </c>
     </row>
     <row r="7">
@@ -589,19 +589,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>17.6502</v>
+        <v>17.38189</v>
       </c>
       <c r="D7" t="n">
-        <v>16.67926</v>
+        <v>16.41064</v>
       </c>
       <c r="E7" t="n">
-        <v>16.8713</v>
+        <v>17.22869</v>
       </c>
       <c r="F7" t="n">
-        <v>23.26167</v>
+        <v>22.44523</v>
       </c>
       <c r="G7" t="n">
-        <v>35.12367</v>
+        <v>35.23857</v>
       </c>
     </row>
     <row r="8">
@@ -611,19 +611,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>17.79167</v>
+        <v>17.34348</v>
       </c>
       <c r="D8" t="n">
-        <v>16.28096</v>
+        <v>16.79922</v>
       </c>
       <c r="E8" t="n">
-        <v>17.26625</v>
+        <v>17.07023</v>
       </c>
       <c r="F8" t="n">
-        <v>22.52885</v>
+        <v>22.44709</v>
       </c>
       <c r="G8" t="n">
-        <v>36.56324</v>
+        <v>35.64128</v>
       </c>
     </row>
   </sheetData>
